--- a/content/Ingeniería de Telecomunicación/Realización de proyectos de ICT/Servicios de radio y TV/Caso_Practico_Tema_3.xlsx
+++ b/content/Ingeniería de Telecomunicación/Realización de proyectos de ICT/Servicios de radio y TV/Caso_Practico_Tema_3.xlsx
@@ -8,9 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\palfa\Documents\GitHub\palfaros-knowledge-base\content\Ingeniería de Telecomunicación\Realización de proyectos de ICT\Servicios de radio y TV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55CE1041-2FDF-4573-A453-863F7FD080DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A5C54B0-9571-40C9-A8BC-81AAF147EFF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" firstSheet="1" activeTab="2" xr2:uid="{05F20D0D-700A-40D6-B3B2-C08799F32B6C}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" firstSheet="1" activeTab="1" xr2:uid="{05F20D0D-700A-40D6-B3B2-C08799F32B6C}"/>
+    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" firstSheet="1" activeTab="2" xr2:uid="{25218655-3AA3-4A01-86F5-3FD4FD14765A}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos" sheetId="1" r:id="rId1"/>
@@ -429,7 +430,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -441,9 +442,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2293,15 +2291,15 @@
     </row>
     <row r="100" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D100" s="2" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F100" s="3">
-        <f>Datos!C$9</f>
-        <v>17</v>
+        <f>Datos!C$6</f>
+        <v>21</v>
       </c>
       <c r="G100" s="3">
-        <f>Datos!D$9</f>
-        <v>17</v>
+        <f>Datos!D$6</f>
+        <v>21</v>
       </c>
     </row>
     <row r="101" spans="3:7" x14ac:dyDescent="0.25">
@@ -2370,11 +2368,11 @@
       </c>
       <c r="F105" s="3">
         <f>SUM(F97:F104)</f>
-        <v>37.306799999999996</v>
+        <v>41.306799999999996</v>
       </c>
       <c r="G105" s="3">
         <f>SUM(G97:G104)</f>
-        <v>37.933499999999995</v>
+        <v>41.933500000000002</v>
       </c>
     </row>
     <row r="106" spans="3:7" x14ac:dyDescent="0.25">
@@ -2431,15 +2429,15 @@
     </row>
     <row r="110" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D110" s="2" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F110" s="3">
-        <f>Datos!C$9</f>
-        <v>17</v>
+        <f>Datos!C$6</f>
+        <v>21</v>
       </c>
       <c r="G110" s="3">
-        <f>Datos!D$9</f>
-        <v>17</v>
+        <f>Datos!D$6</f>
+        <v>21</v>
       </c>
     </row>
     <row r="111" spans="3:7" x14ac:dyDescent="0.25">
@@ -2508,11 +2506,11 @@
       </c>
       <c r="F115" s="3">
         <f>SUM(F107:F114)</f>
-        <v>36.372</v>
+        <v>40.371999999999993</v>
       </c>
       <c r="G115" s="3">
         <f>SUM(G107:G114)</f>
-        <v>36.765000000000001</v>
+        <v>40.765000000000001</v>
       </c>
     </row>
     <row r="116" spans="3:7" x14ac:dyDescent="0.25">
@@ -2569,15 +2567,15 @@
     </row>
     <row r="120" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D120" s="2" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F120" s="3">
-        <f>Datos!C$9</f>
-        <v>17</v>
+        <f>Datos!C$6</f>
+        <v>21</v>
       </c>
       <c r="G120" s="3">
-        <f>Datos!D$9</f>
-        <v>17</v>
+        <f>Datos!D$6</f>
+        <v>21</v>
       </c>
     </row>
     <row r="121" spans="3:7" x14ac:dyDescent="0.25">
@@ -2646,11 +2644,11 @@
       </c>
       <c r="F125" s="3">
         <f>SUM(F117:F124)</f>
-        <v>36.596399999999996</v>
+        <v>40.596399999999996</v>
       </c>
       <c r="G125" s="3">
         <f>SUM(G117:G124)</f>
-        <v>37.045499999999997</v>
+        <v>41.045500000000004</v>
       </c>
     </row>
     <row r="126" spans="3:7" x14ac:dyDescent="0.25">
@@ -2707,15 +2705,15 @@
     </row>
     <row r="130" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D130" s="2" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F130" s="3">
-        <f>Datos!C$9</f>
-        <v>17</v>
+        <f>Datos!C$6</f>
+        <v>21</v>
       </c>
       <c r="G130" s="3">
-        <f>Datos!D$9</f>
-        <v>17</v>
+        <f>Datos!D$6</f>
+        <v>21</v>
       </c>
     </row>
     <row r="131" spans="3:7" x14ac:dyDescent="0.25">
@@ -2784,11 +2782,11 @@
       </c>
       <c r="F135" s="3">
         <f>SUM(F127:F134)</f>
-        <v>36.565199999999997</v>
+        <v>40.565199999999997</v>
       </c>
       <c r="G135" s="3">
         <f>SUM(G127:G134)</f>
-        <v>37.006499999999996</v>
+        <v>41.006500000000003</v>
       </c>
     </row>
     <row r="136" spans="3:7" x14ac:dyDescent="0.25">
@@ -2845,15 +2843,15 @@
     </row>
     <row r="140" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D140" s="2" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F140" s="3">
-        <f>Datos!C$9</f>
-        <v>17</v>
+        <f>Datos!C$6</f>
+        <v>21</v>
       </c>
       <c r="G140" s="3">
-        <f>Datos!D$9</f>
-        <v>17</v>
+        <f>Datos!D$6</f>
+        <v>21</v>
       </c>
     </row>
     <row r="141" spans="3:7" x14ac:dyDescent="0.25">
@@ -2922,11 +2920,11 @@
       </c>
       <c r="F145" s="3">
         <f>SUM(F137:F144)</f>
-        <v>36.4176</v>
+        <v>40.417599999999993</v>
       </c>
       <c r="G145" s="3">
         <f>SUM(G137:G144)</f>
-        <v>36.821999999999996</v>
+        <v>40.822000000000003</v>
       </c>
     </row>
     <row r="146" spans="2:7" x14ac:dyDescent="0.25">
@@ -2988,15 +2986,15 @@
     </row>
     <row r="151" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D151" s="2" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F151" s="3">
-        <f>Datos!C$9</f>
-        <v>17</v>
+        <f>Datos!C$6</f>
+        <v>21</v>
       </c>
       <c r="G151" s="3">
-        <f>Datos!D$9</f>
-        <v>17</v>
+        <f>Datos!D$6</f>
+        <v>21</v>
       </c>
     </row>
     <row r="152" spans="2:7" x14ac:dyDescent="0.25">
@@ -3065,11 +3063,11 @@
       </c>
       <c r="F156" s="3">
         <f>SUM(F148:F155)</f>
-        <v>32.544799999999995</v>
+        <v>36.544799999999995</v>
       </c>
       <c r="G156" s="3">
         <f>SUM(G148:G155)</f>
-        <v>32.980999999999995</v>
+        <v>36.981000000000002</v>
       </c>
     </row>
     <row r="157" spans="2:7" x14ac:dyDescent="0.25">
@@ -3126,15 +3124,15 @@
     </row>
     <row r="161" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D161" s="2" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F161" s="3">
-        <f>Datos!C$9</f>
-        <v>17</v>
+        <f>Datos!C$6</f>
+        <v>21</v>
       </c>
       <c r="G161" s="3">
-        <f>Datos!D$9</f>
-        <v>17</v>
+        <f>Datos!D$6</f>
+        <v>21</v>
       </c>
     </row>
     <row r="162" spans="3:7" x14ac:dyDescent="0.25">
@@ -3203,11 +3201,11 @@
       </c>
       <c r="F166" s="3">
         <f>SUM(F158:F165)</f>
-        <v>32.628799999999998</v>
+        <v>36.628799999999998</v>
       </c>
       <c r="G166" s="3">
         <f>SUM(G158:G165)</f>
-        <v>33.085999999999999</v>
+        <v>37.085999999999999</v>
       </c>
     </row>
     <row r="167" spans="3:7" x14ac:dyDescent="0.25">
@@ -3264,15 +3262,15 @@
     </row>
     <row r="171" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D171" s="2" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F171" s="3">
-        <f>Datos!C$9</f>
-        <v>17</v>
+        <f>Datos!C$6</f>
+        <v>21</v>
       </c>
       <c r="G171" s="3">
-        <f>Datos!D$9</f>
-        <v>17</v>
+        <f>Datos!D$6</f>
+        <v>21</v>
       </c>
     </row>
     <row r="172" spans="3:7" x14ac:dyDescent="0.25">
@@ -3341,11 +3339,11 @@
       </c>
       <c r="F176" s="3">
         <f>SUM(F168:F175)</f>
-        <v>33.179599999999994</v>
+        <v>37.179600000000001</v>
       </c>
       <c r="G176" s="3">
         <f>SUM(G168:G175)</f>
-        <v>33.774500000000003</v>
+        <v>37.774499999999996</v>
       </c>
     </row>
     <row r="177" spans="2:7" x14ac:dyDescent="0.25">
@@ -3402,15 +3400,15 @@
     </row>
     <row r="181" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D181" s="2" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F181" s="3">
-        <f>Datos!C$9</f>
-        <v>17</v>
+        <f>Datos!C$6</f>
+        <v>21</v>
       </c>
       <c r="G181" s="3">
-        <f>Datos!D$9</f>
-        <v>17</v>
+        <f>Datos!D$6</f>
+        <v>21</v>
       </c>
     </row>
     <row r="182" spans="2:7" x14ac:dyDescent="0.25">
@@ -3479,11 +3477,11 @@
       </c>
       <c r="F186" s="3">
         <f>SUM(F178:F185)</f>
-        <v>33.204799999999999</v>
+        <v>37.204799999999999</v>
       </c>
       <c r="G186" s="3">
         <f>SUM(G178:G185)</f>
-        <v>33.805999999999997</v>
+        <v>37.805999999999997</v>
       </c>
     </row>
     <row r="187" spans="2:7" x14ac:dyDescent="0.25">
@@ -3545,15 +3543,15 @@
     </row>
     <row r="192" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D192" s="2" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F192" s="3">
-        <f>Datos!C$9</f>
-        <v>17</v>
+        <f>Datos!C$6</f>
+        <v>21</v>
       </c>
       <c r="G192" s="3">
-        <f>Datos!D$9</f>
-        <v>17</v>
+        <f>Datos!D$6</f>
+        <v>21</v>
       </c>
     </row>
     <row r="193" spans="3:7" x14ac:dyDescent="0.25">
@@ -3622,11 +3620,11 @@
       </c>
       <c r="F197" s="3">
         <f>SUM(F189:F196)</f>
-        <v>37.166399999999996</v>
+        <v>41.166399999999996</v>
       </c>
       <c r="G197" s="3">
         <f>SUM(G189:G196)</f>
-        <v>37.757999999999996</v>
+        <v>41.757999999999996</v>
       </c>
     </row>
     <row r="198" spans="3:7" x14ac:dyDescent="0.25">
@@ -3683,15 +3681,15 @@
     </row>
     <row r="202" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D202" s="2" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F202" s="3">
-        <f>Datos!C$9</f>
-        <v>17</v>
+        <f>Datos!C$6</f>
+        <v>21</v>
       </c>
       <c r="G202" s="3">
-        <f>Datos!D$9</f>
-        <v>17</v>
+        <f>Datos!D$6</f>
+        <v>21</v>
       </c>
     </row>
     <row r="203" spans="3:7" x14ac:dyDescent="0.25">
@@ -3760,11 +3758,11 @@
       </c>
       <c r="F207" s="3">
         <f>SUM(F199:F206)</f>
-        <v>36.6</v>
+        <v>40.6</v>
       </c>
       <c r="G207" s="3">
         <f>SUM(G199:G206)</f>
-        <v>37.049999999999997</v>
+        <v>41.05</v>
       </c>
     </row>
     <row r="208" spans="3:7" x14ac:dyDescent="0.25">
@@ -3821,15 +3819,15 @@
     </row>
     <row r="212" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D212" s="2" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F212" s="3">
-        <f>Datos!C$9</f>
-        <v>17</v>
+        <f>Datos!C$6</f>
+        <v>21</v>
       </c>
       <c r="G212" s="3">
-        <f>Datos!D$9</f>
-        <v>17</v>
+        <f>Datos!D$6</f>
+        <v>21</v>
       </c>
     </row>
     <row r="213" spans="3:7" x14ac:dyDescent="0.25">
@@ -3898,11 +3896,11 @@
       </c>
       <c r="F217" s="3">
         <f>SUM(F209:F216)</f>
-        <v>36.964799999999997</v>
+        <v>40.964799999999997</v>
       </c>
       <c r="G217" s="3">
         <f>SUM(G209:G216)</f>
-        <v>37.505999999999993</v>
+        <v>41.505999999999993</v>
       </c>
     </row>
     <row r="218" spans="3:7" x14ac:dyDescent="0.25">
@@ -3959,15 +3957,15 @@
     </row>
     <row r="222" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D222" s="2" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F222" s="3">
-        <f>Datos!C$9</f>
-        <v>17</v>
+        <f>Datos!C$6</f>
+        <v>21</v>
       </c>
       <c r="G222" s="3">
-        <f>Datos!D$9</f>
-        <v>17</v>
+        <f>Datos!D$6</f>
+        <v>21</v>
       </c>
     </row>
     <row r="223" spans="3:7" x14ac:dyDescent="0.25">
@@ -4036,11 +4034,11 @@
       </c>
       <c r="F227" s="3">
         <f>SUM(F219:F226)</f>
-        <v>37.103999999999999</v>
+        <v>41.103999999999999</v>
       </c>
       <c r="G227" s="3">
         <f>SUM(G219:G226)</f>
-        <v>37.679999999999993</v>
+        <v>41.679999999999993</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
@@ -4097,15 +4095,15 @@
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D232" s="2" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F232" s="3">
-        <f>Datos!C$9</f>
-        <v>17</v>
+        <f>Datos!C$6</f>
+        <v>21</v>
       </c>
       <c r="G232" s="3">
-        <f>Datos!D$9</f>
-        <v>17</v>
+        <f>Datos!D$6</f>
+        <v>21</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
@@ -4174,11 +4172,11 @@
       </c>
       <c r="F237" s="3">
         <f>SUM(F229:F236)</f>
-        <v>37.297199999999997</v>
+        <v>41.297199999999997</v>
       </c>
       <c r="G237" s="3">
         <f>SUM(G229:G236)</f>
-        <v>37.921499999999995</v>
+        <v>41.921499999999995</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
@@ -10645,15 +10643,15 @@
     </row>
     <row r="100" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D100" s="2" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F100" s="3">
-        <f>Datos!C$9</f>
-        <v>17</v>
+        <f>Datos!C$6</f>
+        <v>21</v>
       </c>
       <c r="G100" s="3">
-        <f>Datos!D$9</f>
-        <v>17</v>
+        <f>Datos!D$6</f>
+        <v>21</v>
       </c>
     </row>
     <row r="101" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -10722,11 +10720,11 @@
       </c>
       <c r="F105" s="3">
         <f>SUM(F97:F104)</f>
-        <v>37.306799999999996</v>
+        <v>41.306799999999996</v>
       </c>
       <c r="G105" s="3">
         <f>SUM(G97:G104)</f>
-        <v>37.933499999999995</v>
+        <v>41.933500000000002</v>
       </c>
     </row>
     <row r="106" spans="3:7" x14ac:dyDescent="0.25">
@@ -10783,15 +10781,15 @@
     </row>
     <row r="110" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D110" s="2" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F110" s="3">
-        <f>Datos!C$9</f>
-        <v>17</v>
+        <f>Datos!C$6</f>
+        <v>21</v>
       </c>
       <c r="G110" s="3">
-        <f>Datos!D$9</f>
-        <v>17</v>
+        <f>Datos!D$6</f>
+        <v>21</v>
       </c>
     </row>
     <row r="111" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -10860,11 +10858,11 @@
       </c>
       <c r="F115" s="3">
         <f>SUM(F107:F114)</f>
-        <v>36.372</v>
+        <v>40.371999999999993</v>
       </c>
       <c r="G115" s="3">
         <f>SUM(G107:G114)</f>
-        <v>36.765000000000001</v>
+        <v>40.765000000000001</v>
       </c>
     </row>
     <row r="116" spans="3:7" x14ac:dyDescent="0.25">
@@ -10921,15 +10919,15 @@
     </row>
     <row r="120" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D120" s="2" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F120" s="3">
-        <f>Datos!C$9</f>
-        <v>17</v>
+        <f>Datos!C$6</f>
+        <v>21</v>
       </c>
       <c r="G120" s="3">
-        <f>Datos!D$9</f>
-        <v>17</v>
+        <f>Datos!D$6</f>
+        <v>21</v>
       </c>
     </row>
     <row r="121" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -10998,11 +10996,11 @@
       </c>
       <c r="F125" s="3">
         <f>SUM(F117:F124)</f>
-        <v>36.596399999999996</v>
+        <v>40.596399999999996</v>
       </c>
       <c r="G125" s="3">
         <f>SUM(G117:G124)</f>
-        <v>37.045499999999997</v>
+        <v>41.045500000000004</v>
       </c>
     </row>
     <row r="126" spans="3:7" x14ac:dyDescent="0.25">
@@ -11059,15 +11057,15 @@
     </row>
     <row r="130" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D130" s="2" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F130" s="3">
-        <f>Datos!C$9</f>
-        <v>17</v>
+        <f>Datos!C$6</f>
+        <v>21</v>
       </c>
       <c r="G130" s="3">
-        <f>Datos!D$9</f>
-        <v>17</v>
+        <f>Datos!D$6</f>
+        <v>21</v>
       </c>
     </row>
     <row r="131" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -11136,11 +11134,11 @@
       </c>
       <c r="F135" s="3">
         <f>SUM(F127:F134)</f>
-        <v>36.565199999999997</v>
+        <v>40.565199999999997</v>
       </c>
       <c r="G135" s="3">
         <f>SUM(G127:G134)</f>
-        <v>37.006499999999996</v>
+        <v>41.006500000000003</v>
       </c>
     </row>
     <row r="136" spans="3:7" x14ac:dyDescent="0.25">
@@ -11197,15 +11195,15 @@
     </row>
     <row r="140" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D140" s="2" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F140" s="3">
-        <f>Datos!C$9</f>
-        <v>17</v>
+        <f>Datos!C$6</f>
+        <v>21</v>
       </c>
       <c r="G140" s="3">
-        <f>Datos!D$9</f>
-        <v>17</v>
+        <f>Datos!D$6</f>
+        <v>21</v>
       </c>
     </row>
     <row r="141" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -11274,11 +11272,11 @@
       </c>
       <c r="F145" s="3">
         <f>SUM(F137:F144)</f>
-        <v>36.4176</v>
+        <v>40.417599999999993</v>
       </c>
       <c r="G145" s="3">
         <f>SUM(G137:G144)</f>
-        <v>36.821999999999996</v>
+        <v>40.822000000000003</v>
       </c>
     </row>
     <row r="146" spans="2:7" x14ac:dyDescent="0.25">
@@ -11340,15 +11338,15 @@
     </row>
     <row r="151" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D151" s="2" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F151" s="3">
-        <f>Datos!C$9</f>
-        <v>17</v>
+        <f>Datos!C$6</f>
+        <v>21</v>
       </c>
       <c r="G151" s="3">
-        <f>Datos!D$9</f>
-        <v>17</v>
+        <f>Datos!D$6</f>
+        <v>21</v>
       </c>
     </row>
     <row r="152" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
@@ -11417,11 +11415,11 @@
       </c>
       <c r="F156" s="4">
         <f>SUM(F148:F155)</f>
-        <v>32.544799999999995</v>
-      </c>
-      <c r="G156" s="5">
+        <v>36.544799999999995</v>
+      </c>
+      <c r="G156" s="3">
         <f>SUM(G148:G155)</f>
-        <v>32.980999999999995</v>
+        <v>36.981000000000002</v>
       </c>
     </row>
     <row r="157" spans="2:7" x14ac:dyDescent="0.25">
@@ -11478,15 +11476,15 @@
     </row>
     <row r="161" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D161" s="2" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F161" s="3">
-        <f>Datos!C$9</f>
-        <v>17</v>
+        <f>Datos!C$6</f>
+        <v>21</v>
       </c>
       <c r="G161" s="3">
-        <f>Datos!D$9</f>
-        <v>17</v>
+        <f>Datos!D$6</f>
+        <v>21</v>
       </c>
     </row>
     <row r="162" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -11555,11 +11553,11 @@
       </c>
       <c r="F166" s="3">
         <f>SUM(F158:F165)</f>
-        <v>32.628799999999998</v>
+        <v>36.628799999999998</v>
       </c>
       <c r="G166" s="3">
         <f>SUM(G158:G165)</f>
-        <v>33.085999999999999</v>
+        <v>37.085999999999999</v>
       </c>
     </row>
     <row r="167" spans="3:7" x14ac:dyDescent="0.25">
@@ -11616,15 +11614,15 @@
     </row>
     <row r="171" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D171" s="2" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F171" s="3">
-        <f>Datos!C$9</f>
-        <v>17</v>
+        <f>Datos!C$6</f>
+        <v>21</v>
       </c>
       <c r="G171" s="3">
-        <f>Datos!D$9</f>
-        <v>17</v>
+        <f>Datos!D$6</f>
+        <v>21</v>
       </c>
     </row>
     <row r="172" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -11693,11 +11691,11 @@
       </c>
       <c r="F176" s="3">
         <f>SUM(F168:F175)</f>
-        <v>33.179599999999994</v>
+        <v>37.179600000000001</v>
       </c>
       <c r="G176" s="3">
         <f>SUM(G168:G175)</f>
-        <v>33.774500000000003</v>
+        <v>37.774499999999996</v>
       </c>
     </row>
     <row r="177" spans="2:7" x14ac:dyDescent="0.25">
@@ -11754,15 +11752,15 @@
     </row>
     <row r="181" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D181" s="2" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F181" s="3">
-        <f>Datos!C$9</f>
-        <v>17</v>
+        <f>Datos!C$6</f>
+        <v>21</v>
       </c>
       <c r="G181" s="3">
-        <f>Datos!D$9</f>
-        <v>17</v>
+        <f>Datos!D$6</f>
+        <v>21</v>
       </c>
     </row>
     <row r="182" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
@@ -11831,11 +11829,11 @@
       </c>
       <c r="F186" s="3">
         <f>SUM(F178:F185)</f>
-        <v>33.204799999999999</v>
+        <v>37.204799999999999</v>
       </c>
       <c r="G186" s="3">
         <f>SUM(G178:G185)</f>
-        <v>33.805999999999997</v>
+        <v>37.805999999999997</v>
       </c>
     </row>
     <row r="187" spans="2:7" x14ac:dyDescent="0.25">
@@ -11897,15 +11895,15 @@
     </row>
     <row r="192" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D192" s="2" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F192" s="3">
-        <f>Datos!C$9</f>
-        <v>17</v>
+        <f>Datos!C$6</f>
+        <v>21</v>
       </c>
       <c r="G192" s="3">
-        <f>Datos!D$9</f>
-        <v>17</v>
+        <f>Datos!D$6</f>
+        <v>21</v>
       </c>
     </row>
     <row r="193" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -11974,11 +11972,11 @@
       </c>
       <c r="F197" s="3">
         <f>SUM(F189:F196)</f>
-        <v>37.166399999999996</v>
+        <v>41.166399999999996</v>
       </c>
       <c r="G197" s="3">
         <f>SUM(G189:G196)</f>
-        <v>37.757999999999996</v>
+        <v>41.757999999999996</v>
       </c>
     </row>
     <row r="198" spans="3:7" x14ac:dyDescent="0.25">
@@ -12035,15 +12033,15 @@
     </row>
     <row r="202" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D202" s="2" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F202" s="3">
-        <f>Datos!C$9</f>
-        <v>17</v>
+        <f>Datos!C$6</f>
+        <v>21</v>
       </c>
       <c r="G202" s="3">
-        <f>Datos!D$9</f>
-        <v>17</v>
+        <f>Datos!D$6</f>
+        <v>21</v>
       </c>
     </row>
     <row r="203" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -12112,11 +12110,11 @@
       </c>
       <c r="F207" s="3">
         <f>SUM(F199:F206)</f>
-        <v>36.6</v>
+        <v>40.6</v>
       </c>
       <c r="G207" s="3">
         <f>SUM(G199:G206)</f>
-        <v>37.049999999999997</v>
+        <v>41.05</v>
       </c>
     </row>
     <row r="208" spans="3:7" x14ac:dyDescent="0.25">
@@ -12173,15 +12171,15 @@
     </row>
     <row r="212" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D212" s="2" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F212" s="3">
-        <f>Datos!C$9</f>
-        <v>17</v>
+        <f>Datos!C$6</f>
+        <v>21</v>
       </c>
       <c r="G212" s="3">
-        <f>Datos!D$9</f>
-        <v>17</v>
+        <f>Datos!D$6</f>
+        <v>21</v>
       </c>
     </row>
     <row r="213" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -12250,11 +12248,11 @@
       </c>
       <c r="F217" s="3">
         <f>SUM(F209:F216)</f>
-        <v>36.964799999999997</v>
+        <v>40.964799999999997</v>
       </c>
       <c r="G217" s="3">
         <f>SUM(G209:G216)</f>
-        <v>37.505999999999993</v>
+        <v>41.505999999999993</v>
       </c>
     </row>
     <row r="218" spans="3:7" x14ac:dyDescent="0.25">
@@ -12311,15 +12309,15 @@
     </row>
     <row r="222" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D222" s="2" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F222" s="3">
-        <f>Datos!C$9</f>
-        <v>17</v>
+        <f>Datos!C$6</f>
+        <v>21</v>
       </c>
       <c r="G222" s="3">
-        <f>Datos!D$9</f>
-        <v>17</v>
+        <f>Datos!D$6</f>
+        <v>21</v>
       </c>
     </row>
     <row r="223" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -12388,11 +12386,11 @@
       </c>
       <c r="F227" s="3">
         <f>SUM(F219:F226)</f>
-        <v>37.103999999999999</v>
+        <v>41.103999999999999</v>
       </c>
       <c r="G227" s="3">
         <f>SUM(G219:G226)</f>
-        <v>37.679999999999993</v>
+        <v>41.679999999999993</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
@@ -12449,15 +12447,15 @@
     </row>
     <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D232" s="2" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F232" s="3">
-        <f>Datos!C$9</f>
-        <v>17</v>
+        <f>Datos!C$6</f>
+        <v>21</v>
       </c>
       <c r="G232" s="3">
-        <f>Datos!D$9</f>
-        <v>17</v>
+        <f>Datos!D$6</f>
+        <v>21</v>
       </c>
     </row>
     <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -12526,11 +12524,11 @@
       </c>
       <c r="F237" s="3">
         <f>SUM(F229:F236)</f>
-        <v>37.297199999999997</v>
+        <v>41.297199999999997</v>
       </c>
       <c r="G237" s="3">
         <f>SUM(G229:G236)</f>
-        <v>37.921499999999995</v>
+        <v>41.921499999999995</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
@@ -12702,7 +12700,7 @@
       <c r="D251" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F251" s="5">
+      <c r="F251" s="3">
         <f>SUM(F241:F250)</f>
         <v>40.948799999999999</v>
       </c>
@@ -16099,11 +16097,11 @@
       <c r="D496" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F496" s="5">
+      <c r="F496" s="3">
         <f>SUM(F484:F495)</f>
         <v>35.828800000000001</v>
       </c>
-      <c r="G496" s="5">
+      <c r="G496" s="3">
         <f>SUM(G484:G495)</f>
         <v>36.436</v>
       </c>

--- a/content/Ingeniería de Telecomunicación/Realización de proyectos de ICT/Servicios de radio y TV/Caso_Practico_Tema_3.xlsx
+++ b/content/Ingeniería de Telecomunicación/Realización de proyectos de ICT/Servicios de radio y TV/Caso_Practico_Tema_3.xlsx
@@ -8,10 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\palfa\Documents\GitHub\palfaros-knowledge-base\content\Ingeniería de Telecomunicación\Realización de proyectos de ICT\Servicios de radio y TV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A5C54B0-9571-40C9-A8BC-81AAF147EFF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C28B03CD-5C11-4F4A-BADC-306244EC2455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" firstSheet="1" activeTab="1" xr2:uid="{05F20D0D-700A-40D6-B3B2-C08799F32B6C}"/>
-    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" firstSheet="1" activeTab="2" xr2:uid="{25218655-3AA3-4A01-86F5-3FD4FD14765A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" activeTab="1" xr2:uid="{05F20D0D-700A-40D6-B3B2-C08799F32B6C}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos" sheetId="1" r:id="rId1"/>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="115">
   <si>
     <t>Derivador 544502</t>
   </si>
@@ -347,9 +346,6 @@
     <t>Toma 1, V1, P1</t>
   </si>
   <si>
-    <t>Pérdidas de derivación derivador Televés 5444 (4D)</t>
-  </si>
-  <si>
     <t>Toma 2, V1, P1</t>
   </si>
   <si>
@@ -430,7 +426,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -442,6 +438,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4243,15 +4242,15 @@
     </row>
     <row r="244" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D244" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F244" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G244" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="245" spans="3:7" x14ac:dyDescent="0.25">
@@ -4350,11 +4349,11 @@
       </c>
       <c r="F251" s="3">
         <f>SUM(F241:F250)</f>
-        <v>40.948799999999999</v>
+        <v>38.448800000000006</v>
       </c>
       <c r="G251" s="3">
         <f>SUM(G241:G250)</f>
-        <v>41.661000000000001</v>
+        <v>39.161000000000001</v>
       </c>
     </row>
     <row r="252" spans="3:7" x14ac:dyDescent="0.25">
@@ -4411,15 +4410,15 @@
     </row>
     <row r="256" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D256" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F256" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G256" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="257" spans="3:7" x14ac:dyDescent="0.25">
@@ -4518,11 +4517,11 @@
       </c>
       <c r="F263" s="3">
         <f>SUM(F253:F262)</f>
-        <v>40.013999999999996</v>
+        <v>37.514000000000003</v>
       </c>
       <c r="G263" s="3">
         <f>SUM(G253:G262)</f>
-        <v>40.4925</v>
+        <v>37.9925</v>
       </c>
     </row>
     <row r="264" spans="3:7" x14ac:dyDescent="0.25">
@@ -4579,15 +4578,15 @@
     </row>
     <row r="268" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D268" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F268" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G268" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="269" spans="3:7" x14ac:dyDescent="0.25">
@@ -4686,11 +4685,11 @@
       </c>
       <c r="F275" s="3">
         <f>SUM(F265:F274)</f>
-        <v>40.238399999999999</v>
+        <v>37.738400000000006</v>
       </c>
       <c r="G275" s="3">
         <f>SUM(G265:G274)</f>
-        <v>40.773000000000003</v>
+        <v>38.273000000000003</v>
       </c>
     </row>
     <row r="276" spans="3:7" x14ac:dyDescent="0.25">
@@ -4747,15 +4746,15 @@
     </row>
     <row r="280" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D280" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F280" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G280" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="281" spans="3:7" x14ac:dyDescent="0.25">
@@ -4854,11 +4853,11 @@
       </c>
       <c r="F287" s="3">
         <f>SUM(F277:F286)</f>
-        <v>40.2072</v>
+        <v>37.707200000000007</v>
       </c>
       <c r="G287" s="3">
         <f>SUM(G277:G286)</f>
-        <v>40.734000000000002</v>
+        <v>38.234000000000002</v>
       </c>
     </row>
     <row r="288" spans="3:7" x14ac:dyDescent="0.25">
@@ -4915,15 +4914,15 @@
     </row>
     <row r="292" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D292" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F292" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G292" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="293" spans="2:7" x14ac:dyDescent="0.25">
@@ -5022,11 +5021,11 @@
       </c>
       <c r="F299" s="3">
         <f>SUM(F289:F298)</f>
-        <v>40.059599999999996</v>
+        <v>37.559600000000003</v>
       </c>
       <c r="G299" s="3">
         <f>SUM(G289:G298)</f>
-        <v>40.549500000000002</v>
+        <v>38.049500000000002</v>
       </c>
     </row>
     <row r="300" spans="2:7" x14ac:dyDescent="0.25">
@@ -5088,15 +5087,15 @@
     </row>
     <row r="305" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D305" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F305" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G305" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="306" spans="3:7" x14ac:dyDescent="0.25">
@@ -5195,11 +5194,11 @@
       </c>
       <c r="F312" s="3">
         <f>SUM(F302:F311)</f>
-        <v>36.186799999999998</v>
+        <v>33.686800000000005</v>
       </c>
       <c r="G312" s="3">
         <f>SUM(G302:G311)</f>
-        <v>36.708500000000008</v>
+        <v>34.208500000000001</v>
       </c>
     </row>
     <row r="313" spans="3:7" x14ac:dyDescent="0.25">
@@ -5256,15 +5255,15 @@
     </row>
     <row r="317" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D317" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F317" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G317" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="318" spans="3:7" x14ac:dyDescent="0.25">
@@ -5363,11 +5362,11 @@
       </c>
       <c r="F324" s="3">
         <f>SUM(F314:F323)</f>
-        <v>36.270799999999994</v>
+        <v>33.770800000000001</v>
       </c>
       <c r="G324" s="3">
         <f>SUM(G314:G323)</f>
-        <v>36.813500000000005</v>
+        <v>34.313500000000005</v>
       </c>
     </row>
     <row r="325" spans="3:7" x14ac:dyDescent="0.25">
@@ -5424,15 +5423,15 @@
     </row>
     <row r="329" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D329" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F329" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G329" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="330" spans="3:7" x14ac:dyDescent="0.25">
@@ -5531,11 +5530,11 @@
       </c>
       <c r="F336" s="3">
         <f>SUM(F326:F335)</f>
-        <v>36.821599999999997</v>
+        <v>34.321600000000004</v>
       </c>
       <c r="G336" s="3">
         <f>SUM(G326:G335)</f>
-        <v>37.502000000000002</v>
+        <v>35.002000000000002</v>
       </c>
     </row>
     <row r="337" spans="2:7" x14ac:dyDescent="0.25">
@@ -5592,15 +5591,15 @@
     </row>
     <row r="341" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D341" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F341" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G341" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="342" spans="2:7" x14ac:dyDescent="0.25">
@@ -5699,11 +5698,11 @@
       </c>
       <c r="F348" s="3">
         <f>SUM(F338:F347)</f>
-        <v>36.846799999999995</v>
+        <v>34.346800000000002</v>
       </c>
       <c r="G348" s="3">
         <f>SUM(G338:G347)</f>
-        <v>37.533500000000004</v>
+        <v>35.033500000000004</v>
       </c>
     </row>
     <row r="349" spans="2:7" x14ac:dyDescent="0.25">
@@ -5765,15 +5764,15 @@
     </row>
     <row r="354" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D354" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F354" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G354" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="355" spans="3:7" x14ac:dyDescent="0.25">
@@ -5872,11 +5871,11 @@
       </c>
       <c r="F361" s="3">
         <f>SUM(F351:F360)</f>
-        <v>40.808399999999999</v>
+        <v>38.308399999999999</v>
       </c>
       <c r="G361" s="3">
         <f>SUM(G351:G360)</f>
-        <v>41.485500000000002</v>
+        <v>38.985500000000002</v>
       </c>
     </row>
     <row r="362" spans="3:7" x14ac:dyDescent="0.25">
@@ -5933,15 +5932,15 @@
     </row>
     <row r="366" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D366" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F366" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G366" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="367" spans="3:7" x14ac:dyDescent="0.25">
@@ -6040,11 +6039,11 @@
       </c>
       <c r="F373" s="3">
         <f>SUM(F363:F372)</f>
-        <v>40.242000000000004</v>
+        <v>37.742000000000004</v>
       </c>
       <c r="G373" s="3">
         <f>SUM(G363:G372)</f>
-        <v>40.777500000000003</v>
+        <v>38.277500000000003</v>
       </c>
     </row>
     <row r="374" spans="3:7" x14ac:dyDescent="0.25">
@@ -6101,15 +6100,15 @@
     </row>
     <row r="378" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D378" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F378" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G378" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="379" spans="3:7" x14ac:dyDescent="0.25">
@@ -6208,11 +6207,11 @@
       </c>
       <c r="F385" s="3">
         <f>SUM(F375:F384)</f>
-        <v>40.6068</v>
+        <v>38.1068</v>
       </c>
       <c r="G385" s="3">
         <f>SUM(G375:G384)</f>
-        <v>41.233499999999999</v>
+        <v>38.733499999999999</v>
       </c>
     </row>
     <row r="386" spans="3:7" x14ac:dyDescent="0.25">
@@ -6269,15 +6268,15 @@
     </row>
     <row r="390" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D390" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F390" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G390" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="391" spans="3:7" x14ac:dyDescent="0.25">
@@ -6376,11 +6375,11 @@
       </c>
       <c r="F397" s="3">
         <f>SUM(F387:F396)</f>
-        <v>40.746000000000002</v>
+        <v>38.246000000000002</v>
       </c>
       <c r="G397" s="3">
         <f>SUM(G387:G396)</f>
-        <v>41.407499999999999</v>
+        <v>38.907499999999999</v>
       </c>
     </row>
     <row r="398" spans="3:7" x14ac:dyDescent="0.25">
@@ -6437,15 +6436,15 @@
     </row>
     <row r="402" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D402" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F402" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G402" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.25">
@@ -6544,11 +6543,11 @@
       </c>
       <c r="F409" s="3">
         <f>SUM(F399:F408)</f>
-        <v>40.9392</v>
+        <v>38.4392</v>
       </c>
       <c r="G409" s="3">
         <f>SUM(G399:G408)</f>
-        <v>41.649000000000001</v>
+        <v>39.149000000000001</v>
       </c>
     </row>
     <row r="410" spans="1:7" x14ac:dyDescent="0.25">
@@ -6615,15 +6614,15 @@
     </row>
     <row r="416" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D416" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F416" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G416" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="417" spans="3:7" x14ac:dyDescent="0.25">
@@ -6675,15 +6674,15 @@
     </row>
     <row r="420" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D420" s="2" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="F420" s="3">
-        <f>Datos!C$12</f>
-        <v>13</v>
+        <f>Datos!C$9</f>
+        <v>17</v>
       </c>
       <c r="G420" s="3">
-        <f>Datos!D$12</f>
-        <v>13</v>
+        <f>Datos!D$9</f>
+        <v>17</v>
       </c>
     </row>
     <row r="421" spans="3:7" x14ac:dyDescent="0.25">
@@ -6752,16 +6751,16 @@
       </c>
       <c r="F425" s="3">
         <f>SUM(F413:F424)</f>
-        <v>40.590800000000002</v>
+        <v>42.090800000000002</v>
       </c>
       <c r="G425" s="3">
         <f>SUM(G413:G424)</f>
-        <v>41.388500000000001</v>
+        <v>42.888500000000001</v>
       </c>
     </row>
     <row r="426" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C426" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="427" spans="3:7" x14ac:dyDescent="0.25">
@@ -6813,15 +6812,15 @@
     </row>
     <row r="430" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D430" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F430" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G430" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="431" spans="3:7" x14ac:dyDescent="0.25">
@@ -6873,15 +6872,15 @@
     </row>
     <row r="434" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D434" s="2" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="F434" s="3">
-        <f>Datos!C$12</f>
-        <v>13</v>
+        <f>Datos!C$9</f>
+        <v>17</v>
       </c>
       <c r="G434" s="3">
-        <f>Datos!D$12</f>
-        <v>13</v>
+        <f>Datos!D$9</f>
+        <v>17</v>
       </c>
     </row>
     <row r="435" spans="3:7" x14ac:dyDescent="0.25">
@@ -6950,16 +6949,16 @@
       </c>
       <c r="F439" s="3">
         <f>SUM(F427:F438)</f>
-        <v>39.655999999999999</v>
+        <v>41.155999999999999</v>
       </c>
       <c r="G439" s="3">
         <f>SUM(G427:G438)</f>
-        <v>40.22</v>
+        <v>41.72</v>
       </c>
     </row>
     <row r="440" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C440" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="441" spans="3:7" x14ac:dyDescent="0.25">
@@ -7011,15 +7010,15 @@
     </row>
     <row r="444" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D444" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F444" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G444" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="445" spans="3:7" x14ac:dyDescent="0.25">
@@ -7071,15 +7070,15 @@
     </row>
     <row r="448" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D448" s="2" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="F448" s="3">
-        <f>Datos!C$12</f>
-        <v>13</v>
+        <f>Datos!C$9</f>
+        <v>17</v>
       </c>
       <c r="G448" s="3">
-        <f>Datos!D$12</f>
-        <v>13</v>
+        <f>Datos!D$9</f>
+        <v>17</v>
       </c>
     </row>
     <row r="449" spans="3:7" x14ac:dyDescent="0.25">
@@ -7148,16 +7147,16 @@
       </c>
       <c r="F453" s="3">
         <f>SUM(F441:F452)</f>
-        <v>39.880400000000002</v>
+        <v>41.380400000000002</v>
       </c>
       <c r="G453" s="3">
         <f>SUM(G441:G452)</f>
-        <v>40.500500000000002</v>
+        <v>42.000500000000002</v>
       </c>
     </row>
     <row r="454" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C454" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="455" spans="3:7" x14ac:dyDescent="0.25">
@@ -7209,15 +7208,15 @@
     </row>
     <row r="458" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D458" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F458" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G458" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="459" spans="3:7" x14ac:dyDescent="0.25">
@@ -7269,15 +7268,15 @@
     </row>
     <row r="462" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D462" s="2" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="F462" s="3">
-        <f>Datos!C$12</f>
-        <v>13</v>
+        <f>Datos!C$9</f>
+        <v>17</v>
       </c>
       <c r="G462" s="3">
-        <f>Datos!D$12</f>
-        <v>13</v>
+        <f>Datos!D$9</f>
+        <v>17</v>
       </c>
     </row>
     <row r="463" spans="3:7" x14ac:dyDescent="0.25">
@@ -7346,16 +7345,16 @@
       </c>
       <c r="F467" s="3">
         <f>SUM(F455:F466)</f>
-        <v>39.849200000000003</v>
+        <v>41.349200000000003</v>
       </c>
       <c r="G467" s="3">
         <f>SUM(G455:G466)</f>
-        <v>40.461500000000001</v>
+        <v>41.961500000000001</v>
       </c>
     </row>
     <row r="468" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C468" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="469" spans="3:7" x14ac:dyDescent="0.25">
@@ -7407,15 +7406,15 @@
     </row>
     <row r="472" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D472" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F472" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G472" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="473" spans="3:7" x14ac:dyDescent="0.25">
@@ -7467,15 +7466,15 @@
     </row>
     <row r="476" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D476" s="2" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="F476" s="3">
-        <f>Datos!C$12</f>
-        <v>13</v>
+        <f>Datos!C$9</f>
+        <v>17</v>
       </c>
       <c r="G476" s="3">
-        <f>Datos!D$12</f>
-        <v>13</v>
+        <f>Datos!D$9</f>
+        <v>17</v>
       </c>
     </row>
     <row r="477" spans="3:7" x14ac:dyDescent="0.25">
@@ -7544,11 +7543,11 @@
       </c>
       <c r="F481" s="3">
         <f>SUM(F469:F480)</f>
-        <v>39.701599999999999</v>
+        <v>41.201599999999999</v>
       </c>
       <c r="G481" s="3">
         <f>SUM(G469:G480)</f>
-        <v>40.277000000000001</v>
+        <v>41.777000000000001</v>
       </c>
     </row>
     <row r="482" spans="2:7" x14ac:dyDescent="0.25">
@@ -7558,7 +7557,7 @@
     </row>
     <row r="483" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C483" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="484" spans="2:7" x14ac:dyDescent="0.25">
@@ -7610,15 +7609,15 @@
     </row>
     <row r="487" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D487" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F487" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G487" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="488" spans="2:7" x14ac:dyDescent="0.25">
@@ -7670,15 +7669,15 @@
     </row>
     <row r="491" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D491" s="2" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="F491" s="3">
-        <f>Datos!C$12</f>
-        <v>13</v>
+        <f>Datos!C$9</f>
+        <v>17</v>
       </c>
       <c r="G491" s="3">
-        <f>Datos!D$12</f>
-        <v>13</v>
+        <f>Datos!D$9</f>
+        <v>17</v>
       </c>
     </row>
     <row r="492" spans="2:7" x14ac:dyDescent="0.25">
@@ -7747,16 +7746,16 @@
       </c>
       <c r="F496" s="3">
         <f>SUM(F484:F495)</f>
-        <v>35.828800000000001</v>
+        <v>37.328799999999994</v>
       </c>
       <c r="G496" s="3">
         <f>SUM(G484:G495)</f>
-        <v>36.436</v>
+        <v>37.936</v>
       </c>
     </row>
     <row r="497" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C497" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="498" spans="3:7" x14ac:dyDescent="0.25">
@@ -7808,15 +7807,15 @@
     </row>
     <row r="501" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D501" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F501" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G501" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="502" spans="3:7" x14ac:dyDescent="0.25">
@@ -7868,15 +7867,15 @@
     </row>
     <row r="505" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D505" s="2" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="F505" s="3">
-        <f>Datos!C$12</f>
-        <v>13</v>
+        <f>Datos!C$9</f>
+        <v>17</v>
       </c>
       <c r="G505" s="3">
-        <f>Datos!D$12</f>
-        <v>13</v>
+        <f>Datos!D$9</f>
+        <v>17</v>
       </c>
     </row>
     <row r="506" spans="3:7" x14ac:dyDescent="0.25">
@@ -7945,16 +7944,16 @@
       </c>
       <c r="F510" s="3">
         <f>SUM(F498:F509)</f>
-        <v>35.912800000000004</v>
+        <v>37.412799999999997</v>
       </c>
       <c r="G510" s="3">
         <f>SUM(G498:G509)</f>
-        <v>36.541000000000004</v>
+        <v>38.040999999999997</v>
       </c>
     </row>
     <row r="511" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C511" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="512" spans="3:7" x14ac:dyDescent="0.25">
@@ -8006,15 +8005,15 @@
     </row>
     <row r="515" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D515" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F515" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G515" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="516" spans="3:7" x14ac:dyDescent="0.25">
@@ -8066,15 +8065,15 @@
     </row>
     <row r="519" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D519" s="2" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="F519" s="3">
-        <f>Datos!C$12</f>
-        <v>13</v>
+        <f>Datos!C$9</f>
+        <v>17</v>
       </c>
       <c r="G519" s="3">
-        <f>Datos!D$12</f>
-        <v>13</v>
+        <f>Datos!D$9</f>
+        <v>17</v>
       </c>
     </row>
     <row r="520" spans="3:7" x14ac:dyDescent="0.25">
@@ -8143,16 +8142,16 @@
       </c>
       <c r="F524" s="3">
         <f>SUM(F512:F523)</f>
-        <v>36.4636</v>
+        <v>37.9636</v>
       </c>
       <c r="G524" s="3">
         <f>SUM(G512:G523)</f>
-        <v>37.229500000000002</v>
+        <v>38.729499999999994</v>
       </c>
     </row>
     <row r="525" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C525" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="526" spans="3:7" x14ac:dyDescent="0.25">
@@ -8204,15 +8203,15 @@
     </row>
     <row r="529" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D529" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F529" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G529" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="530" spans="2:7" x14ac:dyDescent="0.25">
@@ -8264,15 +8263,15 @@
     </row>
     <row r="533" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D533" s="2" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="F533" s="3">
-        <f>Datos!C$12</f>
-        <v>13</v>
+        <f>Datos!C$9</f>
+        <v>17</v>
       </c>
       <c r="G533" s="3">
-        <f>Datos!D$12</f>
-        <v>13</v>
+        <f>Datos!D$9</f>
+        <v>17</v>
       </c>
     </row>
     <row r="534" spans="2:7" x14ac:dyDescent="0.25">
@@ -8341,11 +8340,11 @@
       </c>
       <c r="F538" s="3">
         <f>SUM(F526:F537)</f>
-        <v>36.488799999999998</v>
+        <v>37.988799999999998</v>
       </c>
       <c r="G538" s="3">
         <f>SUM(G526:G537)</f>
-        <v>37.261000000000003</v>
+        <v>38.760999999999996</v>
       </c>
     </row>
     <row r="539" spans="2:7" x14ac:dyDescent="0.25">
@@ -8355,7 +8354,7 @@
     </row>
     <row r="540" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C540" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="541" spans="2:7" x14ac:dyDescent="0.25">
@@ -8407,15 +8406,15 @@
     </row>
     <row r="544" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D544" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F544" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G544" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="545" spans="3:7" x14ac:dyDescent="0.25">
@@ -8467,15 +8466,15 @@
     </row>
     <row r="548" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D548" s="2" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="F548" s="3">
-        <f>Datos!C$12</f>
-        <v>13</v>
+        <f>Datos!C$9</f>
+        <v>17</v>
       </c>
       <c r="G548" s="3">
-        <f>Datos!D$12</f>
-        <v>13</v>
+        <f>Datos!D$9</f>
+        <v>17</v>
       </c>
     </row>
     <row r="549" spans="3:7" x14ac:dyDescent="0.25">
@@ -8544,16 +8543,16 @@
       </c>
       <c r="F553" s="3">
         <f>SUM(F541:F552)</f>
-        <v>40.450399999999995</v>
+        <v>41.950399999999995</v>
       </c>
       <c r="G553" s="3">
         <f>SUM(G541:G552)</f>
-        <v>41.213000000000001</v>
+        <v>42.713000000000001</v>
       </c>
     </row>
     <row r="554" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C554" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="555" spans="3:7" x14ac:dyDescent="0.25">
@@ -8605,15 +8604,15 @@
     </row>
     <row r="558" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D558" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F558" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G558" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="559" spans="3:7" x14ac:dyDescent="0.25">
@@ -8665,15 +8664,15 @@
     </row>
     <row r="562" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D562" s="2" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="F562" s="3">
-        <f>Datos!C$12</f>
-        <v>13</v>
+        <f>Datos!C$9</f>
+        <v>17</v>
       </c>
       <c r="G562" s="3">
-        <f>Datos!D$12</f>
-        <v>13</v>
+        <f>Datos!D$9</f>
+        <v>17</v>
       </c>
     </row>
     <row r="563" spans="3:7" x14ac:dyDescent="0.25">
@@ -8742,16 +8741,16 @@
       </c>
       <c r="F567" s="3">
         <f>SUM(F555:F566)</f>
-        <v>39.884</v>
+        <v>41.384</v>
       </c>
       <c r="G567" s="3">
         <f>SUM(G555:G566)</f>
-        <v>40.505000000000003</v>
+        <v>42.005000000000003</v>
       </c>
     </row>
     <row r="568" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C568" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="569" spans="3:7" x14ac:dyDescent="0.25">
@@ -8803,15 +8802,15 @@
     </row>
     <row r="572" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D572" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F572" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G572" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="573" spans="3:7" x14ac:dyDescent="0.25">
@@ -8863,15 +8862,15 @@
     </row>
     <row r="576" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D576" s="2" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="F576" s="3">
-        <f>Datos!C$12</f>
-        <v>13</v>
+        <f>Datos!C$9</f>
+        <v>17</v>
       </c>
       <c r="G576" s="3">
-        <f>Datos!D$12</f>
-        <v>13</v>
+        <f>Datos!D$9</f>
+        <v>17</v>
       </c>
     </row>
     <row r="577" spans="3:7" x14ac:dyDescent="0.25">
@@ -8940,16 +8939,16 @@
       </c>
       <c r="F581" s="3">
         <f>SUM(F569:F580)</f>
-        <v>40.248799999999996</v>
+        <v>41.748799999999996</v>
       </c>
       <c r="G581" s="3">
         <f>SUM(G569:G580)</f>
-        <v>40.960999999999999</v>
+        <v>42.460999999999999</v>
       </c>
     </row>
     <row r="582" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C582" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="583" spans="3:7" x14ac:dyDescent="0.25">
@@ -9001,15 +9000,15 @@
     </row>
     <row r="586" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D586" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F586" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G586" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="587" spans="3:7" x14ac:dyDescent="0.25">
@@ -9061,15 +9060,15 @@
     </row>
     <row r="590" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D590" s="2" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="F590" s="3">
-        <f>Datos!C$12</f>
-        <v>13</v>
+        <f>Datos!C$9</f>
+        <v>17</v>
       </c>
       <c r="G590" s="3">
-        <f>Datos!D$12</f>
-        <v>13</v>
+        <f>Datos!D$9</f>
+        <v>17</v>
       </c>
     </row>
     <row r="591" spans="3:7" x14ac:dyDescent="0.25">
@@ -9138,16 +9137,16 @@
       </c>
       <c r="F595" s="3">
         <f>SUM(F583:F594)</f>
-        <v>40.387999999999998</v>
+        <v>41.887999999999998</v>
       </c>
       <c r="G595" s="3">
         <f>SUM(G583:G594)</f>
-        <v>41.134999999999998</v>
+        <v>42.634999999999998</v>
       </c>
     </row>
     <row r="596" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C596" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="597" spans="3:7" x14ac:dyDescent="0.25">
@@ -9199,15 +9198,15 @@
     </row>
     <row r="600" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D600" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F600" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G600" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="601" spans="3:7" x14ac:dyDescent="0.25">
@@ -9259,15 +9258,15 @@
     </row>
     <row r="604" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D604" s="2" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="F604" s="3">
-        <f>Datos!C$12</f>
-        <v>13</v>
+        <f>Datos!C$9</f>
+        <v>17</v>
       </c>
       <c r="G604" s="3">
-        <f>Datos!D$12</f>
-        <v>13</v>
+        <f>Datos!D$9</f>
+        <v>17</v>
       </c>
     </row>
     <row r="605" spans="3:7" x14ac:dyDescent="0.25">
@@ -9336,11 +9335,11 @@
       </c>
       <c r="F609" s="3">
         <f>SUM(F597:F608)</f>
-        <v>40.581199999999995</v>
+        <v>42.081199999999995</v>
       </c>
       <c r="G609" s="3">
         <f>SUM(G597:G608)</f>
-        <v>41.3765</v>
+        <v>42.8765</v>
       </c>
     </row>
   </sheetData>
@@ -11413,7 +11412,7 @@
       <c r="D156" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F156" s="4">
+      <c r="F156" s="5">
         <f>SUM(F148:F155)</f>
         <v>36.544799999999995</v>
       </c>
@@ -12595,15 +12594,15 @@
     </row>
     <row r="244" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D244" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F244" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G244" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="245" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -12702,11 +12701,11 @@
       </c>
       <c r="F251" s="3">
         <f>SUM(F241:F250)</f>
-        <v>40.948799999999999</v>
-      </c>
-      <c r="G251" s="4">
+        <v>38.448800000000006</v>
+      </c>
+      <c r="G251" s="5">
         <f>SUM(G241:G250)</f>
-        <v>41.661000000000001</v>
+        <v>39.161000000000001</v>
       </c>
     </row>
     <row r="252" spans="3:7" x14ac:dyDescent="0.25">
@@ -12763,15 +12762,15 @@
     </row>
     <row r="256" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D256" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F256" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G256" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="257" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -12870,11 +12869,11 @@
       </c>
       <c r="F263" s="3">
         <f>SUM(F253:F262)</f>
-        <v>40.013999999999996</v>
+        <v>37.514000000000003</v>
       </c>
       <c r="G263" s="3">
         <f>SUM(G253:G262)</f>
-        <v>40.4925</v>
+        <v>37.9925</v>
       </c>
     </row>
     <row r="264" spans="3:7" x14ac:dyDescent="0.25">
@@ -12931,15 +12930,15 @@
     </row>
     <row r="268" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D268" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F268" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G268" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="269" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -13038,11 +13037,11 @@
       </c>
       <c r="F275" s="3">
         <f>SUM(F265:F274)</f>
-        <v>40.238399999999999</v>
+        <v>37.738400000000006</v>
       </c>
       <c r="G275" s="3">
         <f>SUM(G265:G274)</f>
-        <v>40.773000000000003</v>
+        <v>38.273000000000003</v>
       </c>
     </row>
     <row r="276" spans="3:7" x14ac:dyDescent="0.25">
@@ -13099,15 +13098,15 @@
     </row>
     <row r="280" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D280" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F280" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G280" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="281" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -13206,11 +13205,11 @@
       </c>
       <c r="F287" s="3">
         <f>SUM(F277:F286)</f>
-        <v>40.2072</v>
+        <v>37.707200000000007</v>
       </c>
       <c r="G287" s="3">
         <f>SUM(G277:G286)</f>
-        <v>40.734000000000002</v>
+        <v>38.234000000000002</v>
       </c>
     </row>
     <row r="288" spans="3:7" x14ac:dyDescent="0.25">
@@ -13267,15 +13266,15 @@
     </row>
     <row r="292" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D292" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F292" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G292" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="293" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
@@ -13374,11 +13373,11 @@
       </c>
       <c r="F299" s="3">
         <f>SUM(F289:F298)</f>
-        <v>40.059599999999996</v>
+        <v>37.559600000000003</v>
       </c>
       <c r="G299" s="3">
         <f>SUM(G289:G298)</f>
-        <v>40.549500000000002</v>
+        <v>38.049500000000002</v>
       </c>
     </row>
     <row r="300" spans="2:7" x14ac:dyDescent="0.25">
@@ -13440,15 +13439,15 @@
     </row>
     <row r="305" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D305" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F305" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G305" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="306" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -13545,13 +13544,13 @@
       <c r="D312" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F312" s="3">
+      <c r="F312" s="4">
         <f>SUM(F302:F311)</f>
-        <v>36.186799999999998</v>
+        <v>33.686800000000005</v>
       </c>
       <c r="G312" s="3">
         <f>SUM(G302:G311)</f>
-        <v>36.708500000000008</v>
+        <v>34.208500000000001</v>
       </c>
     </row>
     <row r="313" spans="3:7" x14ac:dyDescent="0.25">
@@ -13608,15 +13607,15 @@
     </row>
     <row r="317" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D317" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F317" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G317" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="318" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -13715,11 +13714,11 @@
       </c>
       <c r="F324" s="3">
         <f>SUM(F314:F323)</f>
-        <v>36.270799999999994</v>
+        <v>33.770800000000001</v>
       </c>
       <c r="G324" s="3">
         <f>SUM(G314:G323)</f>
-        <v>36.813500000000005</v>
+        <v>34.313500000000005</v>
       </c>
     </row>
     <row r="325" spans="3:7" x14ac:dyDescent="0.25">
@@ -13776,15 +13775,15 @@
     </row>
     <row r="329" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D329" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F329" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G329" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="330" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -13883,11 +13882,11 @@
       </c>
       <c r="F336" s="3">
         <f>SUM(F326:F335)</f>
-        <v>36.821599999999997</v>
+        <v>34.321600000000004</v>
       </c>
       <c r="G336" s="3">
         <f>SUM(G326:G335)</f>
-        <v>37.502000000000002</v>
+        <v>35.002000000000002</v>
       </c>
     </row>
     <row r="337" spans="2:7" x14ac:dyDescent="0.25">
@@ -13944,15 +13943,15 @@
     </row>
     <row r="341" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D341" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F341" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G341" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="342" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
@@ -14051,11 +14050,11 @@
       </c>
       <c r="F348" s="3">
         <f>SUM(F338:F347)</f>
-        <v>36.846799999999995</v>
+        <v>34.346800000000002</v>
       </c>
       <c r="G348" s="3">
         <f>SUM(G338:G347)</f>
-        <v>37.533500000000004</v>
+        <v>35.033500000000004</v>
       </c>
     </row>
     <row r="349" spans="2:7" x14ac:dyDescent="0.25">
@@ -14117,15 +14116,15 @@
     </row>
     <row r="354" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D354" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F354" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G354" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="355" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -14224,11 +14223,11 @@
       </c>
       <c r="F361" s="3">
         <f>SUM(F351:F360)</f>
-        <v>40.808399999999999</v>
+        <v>38.308399999999999</v>
       </c>
       <c r="G361" s="3">
         <f>SUM(G351:G360)</f>
-        <v>41.485500000000002</v>
+        <v>38.985500000000002</v>
       </c>
     </row>
     <row r="362" spans="3:7" x14ac:dyDescent="0.25">
@@ -14285,15 +14284,15 @@
     </row>
     <row r="366" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D366" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F366" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G366" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="367" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -14392,11 +14391,11 @@
       </c>
       <c r="F373" s="3">
         <f>SUM(F363:F372)</f>
-        <v>40.242000000000004</v>
+        <v>37.742000000000004</v>
       </c>
       <c r="G373" s="3">
         <f>SUM(G363:G372)</f>
-        <v>40.777500000000003</v>
+        <v>38.277500000000003</v>
       </c>
     </row>
     <row r="374" spans="3:7" x14ac:dyDescent="0.25">
@@ -14453,15 +14452,15 @@
     </row>
     <row r="378" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D378" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F378" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G378" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="379" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -14560,11 +14559,11 @@
       </c>
       <c r="F385" s="3">
         <f>SUM(F375:F384)</f>
-        <v>40.6068</v>
+        <v>38.1068</v>
       </c>
       <c r="G385" s="3">
         <f>SUM(G375:G384)</f>
-        <v>41.233499999999999</v>
+        <v>38.733499999999999</v>
       </c>
     </row>
     <row r="386" spans="3:7" x14ac:dyDescent="0.25">
@@ -14621,15 +14620,15 @@
     </row>
     <row r="390" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D390" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F390" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G390" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="391" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -14728,11 +14727,11 @@
       </c>
       <c r="F397" s="3">
         <f>SUM(F387:F396)</f>
-        <v>40.746000000000002</v>
+        <v>38.246000000000002</v>
       </c>
       <c r="G397" s="3">
         <f>SUM(G387:G396)</f>
-        <v>41.407499999999999</v>
+        <v>38.907499999999999</v>
       </c>
     </row>
     <row r="398" spans="3:7" x14ac:dyDescent="0.25">
@@ -14789,15 +14788,15 @@
     </row>
     <row r="402" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D402" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F402" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G402" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="403" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -14896,11 +14895,11 @@
       </c>
       <c r="F409" s="3">
         <f>SUM(F399:F408)</f>
-        <v>40.9392</v>
+        <v>38.4392</v>
       </c>
       <c r="G409" s="3">
         <f>SUM(G399:G408)</f>
-        <v>41.649000000000001</v>
+        <v>39.149000000000001</v>
       </c>
     </row>
     <row r="410" spans="1:7" x14ac:dyDescent="0.25">
@@ -14967,15 +14966,15 @@
     </row>
     <row r="416" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D416" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F416" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G416" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="417" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -15027,15 +15026,15 @@
     </row>
     <row r="420" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D420" s="2" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="F420" s="3">
-        <f>Datos!C$12</f>
-        <v>13</v>
+        <f>Datos!C$9</f>
+        <v>17</v>
       </c>
       <c r="G420" s="3">
-        <f>Datos!D$12</f>
-        <v>13</v>
+        <f>Datos!D$9</f>
+        <v>17</v>
       </c>
     </row>
     <row r="421" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -15104,16 +15103,16 @@
       </c>
       <c r="F425" s="3">
         <f>SUM(F413:F424)</f>
-        <v>40.590800000000002</v>
-      </c>
-      <c r="G425" s="3">
+        <v>42.090800000000002</v>
+      </c>
+      <c r="G425" s="4">
         <f>SUM(G413:G424)</f>
-        <v>41.388500000000001</v>
+        <v>42.888500000000001</v>
       </c>
     </row>
     <row r="426" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C426" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="427" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -15165,15 +15164,15 @@
     </row>
     <row r="430" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D430" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F430" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G430" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="431" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -15225,15 +15224,15 @@
     </row>
     <row r="434" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D434" s="2" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="F434" s="3">
-        <f>Datos!C$12</f>
-        <v>13</v>
+        <f>Datos!C$9</f>
+        <v>17</v>
       </c>
       <c r="G434" s="3">
-        <f>Datos!D$12</f>
-        <v>13</v>
+        <f>Datos!D$9</f>
+        <v>17</v>
       </c>
     </row>
     <row r="435" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -15302,16 +15301,16 @@
       </c>
       <c r="F439" s="3">
         <f>SUM(F427:F438)</f>
-        <v>39.655999999999999</v>
+        <v>41.155999999999999</v>
       </c>
       <c r="G439" s="3">
         <f>SUM(G427:G438)</f>
-        <v>40.22</v>
+        <v>41.72</v>
       </c>
     </row>
     <row r="440" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C440" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="441" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -15363,15 +15362,15 @@
     </row>
     <row r="444" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D444" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F444" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G444" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="445" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -15423,15 +15422,15 @@
     </row>
     <row r="448" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D448" s="2" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="F448" s="3">
-        <f>Datos!C$12</f>
-        <v>13</v>
+        <f>Datos!C$9</f>
+        <v>17</v>
       </c>
       <c r="G448" s="3">
-        <f>Datos!D$12</f>
-        <v>13</v>
+        <f>Datos!D$9</f>
+        <v>17</v>
       </c>
     </row>
     <row r="449" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -15500,16 +15499,16 @@
       </c>
       <c r="F453" s="3">
         <f>SUM(F441:F452)</f>
-        <v>39.880400000000002</v>
+        <v>41.380400000000002</v>
       </c>
       <c r="G453" s="3">
         <f>SUM(G441:G452)</f>
-        <v>40.500500000000002</v>
+        <v>42.000500000000002</v>
       </c>
     </row>
     <row r="454" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C454" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="455" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -15561,15 +15560,15 @@
     </row>
     <row r="458" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D458" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F458" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G458" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="459" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -15621,15 +15620,15 @@
     </row>
     <row r="462" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D462" s="2" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="F462" s="3">
-        <f>Datos!C$12</f>
-        <v>13</v>
+        <f>Datos!C$9</f>
+        <v>17</v>
       </c>
       <c r="G462" s="3">
-        <f>Datos!D$12</f>
-        <v>13</v>
+        <f>Datos!D$9</f>
+        <v>17</v>
       </c>
     </row>
     <row r="463" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -15698,16 +15697,16 @@
       </c>
       <c r="F467" s="3">
         <f>SUM(F455:F466)</f>
-        <v>39.849200000000003</v>
+        <v>41.349200000000003</v>
       </c>
       <c r="G467" s="3">
         <f>SUM(G455:G466)</f>
-        <v>40.461500000000001</v>
+        <v>41.961500000000001</v>
       </c>
     </row>
     <row r="468" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C468" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="469" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -15759,15 +15758,15 @@
     </row>
     <row r="472" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D472" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F472" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G472" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="473" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -15819,15 +15818,15 @@
     </row>
     <row r="476" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D476" s="2" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="F476" s="3">
-        <f>Datos!C$12</f>
-        <v>13</v>
+        <f>Datos!C$9</f>
+        <v>17</v>
       </c>
       <c r="G476" s="3">
-        <f>Datos!D$12</f>
-        <v>13</v>
+        <f>Datos!D$9</f>
+        <v>17</v>
       </c>
     </row>
     <row r="477" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -15896,11 +15895,11 @@
       </c>
       <c r="F481" s="3">
         <f>SUM(F469:F480)</f>
-        <v>39.701599999999999</v>
+        <v>41.201599999999999</v>
       </c>
       <c r="G481" s="3">
         <f>SUM(G469:G480)</f>
-        <v>40.277000000000001</v>
+        <v>41.777000000000001</v>
       </c>
     </row>
     <row r="482" spans="2:7" x14ac:dyDescent="0.25">
@@ -15910,7 +15909,7 @@
     </row>
     <row r="483" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C483" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="484" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
@@ -15962,15 +15961,15 @@
     </row>
     <row r="487" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D487" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F487" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G487" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="488" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
@@ -16022,15 +16021,15 @@
     </row>
     <row r="491" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D491" s="2" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="F491" s="3">
-        <f>Datos!C$12</f>
-        <v>13</v>
+        <f>Datos!C$9</f>
+        <v>17</v>
       </c>
       <c r="G491" s="3">
-        <f>Datos!D$12</f>
-        <v>13</v>
+        <f>Datos!D$9</f>
+        <v>17</v>
       </c>
     </row>
     <row r="492" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
@@ -16099,16 +16098,16 @@
       </c>
       <c r="F496" s="3">
         <f>SUM(F484:F495)</f>
-        <v>35.828800000000001</v>
+        <v>37.328799999999994</v>
       </c>
       <c r="G496" s="3">
         <f>SUM(G484:G495)</f>
-        <v>36.436</v>
+        <v>37.936</v>
       </c>
     </row>
     <row r="497" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C497" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="498" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -16160,15 +16159,15 @@
     </row>
     <row r="501" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D501" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F501" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G501" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="502" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -16220,15 +16219,15 @@
     </row>
     <row r="505" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D505" s="2" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="F505" s="3">
-        <f>Datos!C$12</f>
-        <v>13</v>
+        <f>Datos!C$9</f>
+        <v>17</v>
       </c>
       <c r="G505" s="3">
-        <f>Datos!D$12</f>
-        <v>13</v>
+        <f>Datos!D$9</f>
+        <v>17</v>
       </c>
     </row>
     <row r="506" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -16297,16 +16296,16 @@
       </c>
       <c r="F510" s="3">
         <f>SUM(F498:F509)</f>
-        <v>35.912800000000004</v>
+        <v>37.412799999999997</v>
       </c>
       <c r="G510" s="3">
         <f>SUM(G498:G509)</f>
-        <v>36.541000000000004</v>
+        <v>38.040999999999997</v>
       </c>
     </row>
     <row r="511" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C511" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="512" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -16358,15 +16357,15 @@
     </row>
     <row r="515" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D515" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F515" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G515" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="516" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -16418,15 +16417,15 @@
     </row>
     <row r="519" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D519" s="2" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="F519" s="3">
-        <f>Datos!C$12</f>
-        <v>13</v>
+        <f>Datos!C$9</f>
+        <v>17</v>
       </c>
       <c r="G519" s="3">
-        <f>Datos!D$12</f>
-        <v>13</v>
+        <f>Datos!D$9</f>
+        <v>17</v>
       </c>
     </row>
     <row r="520" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -16495,16 +16494,16 @@
       </c>
       <c r="F524" s="3">
         <f>SUM(F512:F523)</f>
-        <v>36.4636</v>
+        <v>37.9636</v>
       </c>
       <c r="G524" s="3">
         <f>SUM(G512:G523)</f>
-        <v>37.229500000000002</v>
+        <v>38.729499999999994</v>
       </c>
     </row>
     <row r="525" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C525" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="526" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -16556,15 +16555,15 @@
     </row>
     <row r="529" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D529" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F529" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G529" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="530" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
@@ -16616,15 +16615,15 @@
     </row>
     <row r="533" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D533" s="2" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="F533" s="3">
-        <f>Datos!C$12</f>
-        <v>13</v>
+        <f>Datos!C$9</f>
+        <v>17</v>
       </c>
       <c r="G533" s="3">
-        <f>Datos!D$12</f>
-        <v>13</v>
+        <f>Datos!D$9</f>
+        <v>17</v>
       </c>
     </row>
     <row r="534" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
@@ -16693,11 +16692,11 @@
       </c>
       <c r="F538" s="3">
         <f>SUM(F526:F537)</f>
-        <v>36.488799999999998</v>
+        <v>37.988799999999998</v>
       </c>
       <c r="G538" s="3">
         <f>SUM(G526:G537)</f>
-        <v>37.261000000000003</v>
+        <v>38.760999999999996</v>
       </c>
     </row>
     <row r="539" spans="2:7" x14ac:dyDescent="0.25">
@@ -16707,7 +16706,7 @@
     </row>
     <row r="540" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C540" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="541" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
@@ -16759,15 +16758,15 @@
     </row>
     <row r="544" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D544" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F544" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G544" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="545" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -16819,15 +16818,15 @@
     </row>
     <row r="548" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D548" s="2" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="F548" s="3">
-        <f>Datos!C$12</f>
-        <v>13</v>
+        <f>Datos!C$9</f>
+        <v>17</v>
       </c>
       <c r="G548" s="3">
-        <f>Datos!D$12</f>
-        <v>13</v>
+        <f>Datos!D$9</f>
+        <v>17</v>
       </c>
     </row>
     <row r="549" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -16896,16 +16895,16 @@
       </c>
       <c r="F553" s="3">
         <f>SUM(F541:F552)</f>
-        <v>40.450399999999995</v>
+        <v>41.950399999999995</v>
       </c>
       <c r="G553" s="3">
         <f>SUM(G541:G552)</f>
-        <v>41.213000000000001</v>
+        <v>42.713000000000001</v>
       </c>
     </row>
     <row r="554" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C554" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="555" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -16957,15 +16956,15 @@
     </row>
     <row r="558" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D558" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F558" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G558" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="559" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -17017,15 +17016,15 @@
     </row>
     <row r="562" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D562" s="2" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="F562" s="3">
-        <f>Datos!C$12</f>
-        <v>13</v>
+        <f>Datos!C$9</f>
+        <v>17</v>
       </c>
       <c r="G562" s="3">
-        <f>Datos!D$12</f>
-        <v>13</v>
+        <f>Datos!D$9</f>
+        <v>17</v>
       </c>
     </row>
     <row r="563" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -17094,16 +17093,16 @@
       </c>
       <c r="F567" s="3">
         <f>SUM(F555:F566)</f>
-        <v>39.884</v>
+        <v>41.384</v>
       </c>
       <c r="G567" s="3">
         <f>SUM(G555:G566)</f>
-        <v>40.505000000000003</v>
+        <v>42.005000000000003</v>
       </c>
     </row>
     <row r="568" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C568" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="569" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -17155,15 +17154,15 @@
     </row>
     <row r="572" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D572" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F572" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G572" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="573" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -17215,15 +17214,15 @@
     </row>
     <row r="576" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D576" s="2" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="F576" s="3">
-        <f>Datos!C$12</f>
-        <v>13</v>
+        <f>Datos!C$9</f>
+        <v>17</v>
       </c>
       <c r="G576" s="3">
-        <f>Datos!D$12</f>
-        <v>13</v>
+        <f>Datos!D$9</f>
+        <v>17</v>
       </c>
     </row>
     <row r="577" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -17292,16 +17291,16 @@
       </c>
       <c r="F581" s="3">
         <f>SUM(F569:F580)</f>
-        <v>40.248799999999996</v>
+        <v>41.748799999999996</v>
       </c>
       <c r="G581" s="3">
         <f>SUM(G569:G580)</f>
-        <v>40.960999999999999</v>
+        <v>42.460999999999999</v>
       </c>
     </row>
     <row r="582" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C582" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="583" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -17353,15 +17352,15 @@
     </row>
     <row r="586" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D586" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F586" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G586" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="587" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -17413,15 +17412,15 @@
     </row>
     <row r="590" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D590" s="2" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="F590" s="3">
-        <f>Datos!C$12</f>
-        <v>13</v>
+        <f>Datos!C$9</f>
+        <v>17</v>
       </c>
       <c r="G590" s="3">
-        <f>Datos!D$12</f>
-        <v>13</v>
+        <f>Datos!D$9</f>
+        <v>17</v>
       </c>
     </row>
     <row r="591" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -17490,16 +17489,16 @@
       </c>
       <c r="F595" s="3">
         <f>SUM(F583:F594)</f>
-        <v>40.387999999999998</v>
+        <v>41.887999999999998</v>
       </c>
       <c r="G595" s="3">
         <f>SUM(G583:G594)</f>
-        <v>41.134999999999998</v>
+        <v>42.634999999999998</v>
       </c>
     </row>
     <row r="596" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C596" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="597" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -17551,15 +17550,15 @@
     </row>
     <row r="600" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D600" s="2" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F600" s="3">
-        <f>Datos!C$8</f>
-        <v>3.3</v>
+        <f>Datos!C$5</f>
+        <v>0.8</v>
       </c>
       <c r="G600" s="3">
-        <f>Datos!D$8</f>
-        <v>3.3</v>
+        <f>Datos!D$5</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="601" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -17611,15 +17610,15 @@
     </row>
     <row r="604" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="D604" s="2" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="F604" s="3">
-        <f>Datos!C$12</f>
-        <v>13</v>
+        <f>Datos!C$9</f>
+        <v>17</v>
       </c>
       <c r="G604" s="3">
-        <f>Datos!D$12</f>
-        <v>13</v>
+        <f>Datos!D$9</f>
+        <v>17</v>
       </c>
     </row>
     <row r="605" spans="3:7" hidden="1" x14ac:dyDescent="0.25">
@@ -17688,11 +17687,11 @@
       </c>
       <c r="F609" s="3">
         <f>SUM(F597:F608)</f>
-        <v>40.581199999999995</v>
+        <v>42.081199999999995</v>
       </c>
       <c r="G609" s="3">
         <f>SUM(G597:G608)</f>
-        <v>41.3765</v>
+        <v>42.8765</v>
       </c>
     </row>
   </sheetData>
